--- a/lime-house/referral-nagano/LIME_HOUSE_フェイスシート_長野太吉様.xlsx
+++ b/lime-house/referral-nagano/LIME_HOUSE_フェイスシート_長野太吉様.xlsx
@@ -2014,7 +2014,7 @@
     <mergeCell ref="C65:E65"/>
     <mergeCell ref="C47:E47"/>
   </mergeCells>
-  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.8" header="0.5" footer="0.35"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
